--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-04 09:46 UTC · 87 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 74 ms</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10200210.66</v>
+        <v>10200365.31</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-5068938.23</v>
+        <v>-1043813.17</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>607.35</v>
+        <v>607.28</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-406.32</v>
+        <v>-48.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.42</v>
+        <v>-0.17</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.101</v>
+        <v>-0.0199</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -655,11 +655,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.101</v>
+        <v>-0.0199</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -678,11 +678,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2369</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -701,11 +701,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.2369</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -724,11 +724,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1273</v>
+        <v>0.0012</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -940,23 +940,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Port Province</t>
+          <t>National Capital District</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>168000</v>
       </c>
       <c r="E2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="F2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>218110.94</v>
+        <v>218269.16</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -980,7 +980,7 @@
         <v>0.08</v>
       </c>
       <c r="N2" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="O2" t="n">
         <v>0.0262</v>
@@ -1024,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>173548.04</v>
+        <v>173529.48</v>
       </c>
       <c r="I3" t="n">
         <v>1.31</v>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>78980.13</v>
+        <v>78971.56</v>
       </c>
       <c r="I4" t="n">
         <v>1.29</v>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>70256.22</v>
+        <v>70248.62</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>49813.59</v>
+        <v>49808.25</v>
       </c>
       <c r="I6" t="n">
         <v>1.31</v>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>70037.50999999999</v>
+        <v>70030.89999999999</v>
       </c>
       <c r="I7" t="n">
         <v>1.49</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>71652.41</v>
+        <v>71646.50999999999</v>
       </c>
       <c r="I8" t="n">
         <v>1.71</v>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>33442.78</v>
+        <v>33440.1</v>
       </c>
       <c r="I9" t="n">
         <v>1.76</v>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>62297.7</v>
+        <v>62292.36</v>
       </c>
       <c r="I10" t="n">
         <v>1.64</v>
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>127569.05</v>
+        <v>127567.37</v>
       </c>
       <c r="I11" t="n">
         <v>10.63</v>
@@ -1636,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>25615.8</v>
+        <v>25613.55</v>
       </c>
       <c r="I12" t="n">
         <v>1.6</v>
@@ -1704,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>110967.18</v>
+        <v>110959.02</v>
       </c>
       <c r="I13" t="n">
         <v>1.91</v>
@@ -1772,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>37548.93</v>
+        <v>37545.98</v>
       </c>
       <c r="I14" t="n">
         <v>1.79</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>57217.42</v>
+        <v>57212.92</v>
       </c>
       <c r="I15" t="n">
         <v>1.79</v>
@@ -1908,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>32184.8</v>
+        <v>32182.27</v>
       </c>
       <c r="I16" t="n">
         <v>1.79</v>
@@ -1976,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>46696.88</v>
+        <v>46693.51</v>
       </c>
       <c r="I17" t="n">
         <v>1.95</v>
@@ -2107,7 +2107,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>81994.05</v>
+        <v>81987.86</v>
       </c>
       <c r="I19" t="n">
         <v>1.86</v>
@@ -2175,7 +2175,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>70475.50999999999</v>
+        <v>70470.03</v>
       </c>
       <c r="I20" t="n">
         <v>1.81</v>
@@ -2243,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>50597.8</v>
+        <v>50593.87</v>
       </c>
       <c r="I21" t="n">
         <v>1.81</v>
@@ -2311,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>56019</v>
+        <v>56014.64</v>
       </c>
       <c r="I22" t="n">
         <v>1.81</v>
@@ -2379,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>97422.56</v>
+        <v>97421.3</v>
       </c>
       <c r="I23" t="n">
         <v>10.82</v>
@@ -2447,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>92010.2</v>
+        <v>92009</v>
       </c>
       <c r="I24" t="n">
         <v>10.82</v>
@@ -2515,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>13552.98</v>
+        <v>13551.93</v>
       </c>
       <c r="I25" t="n">
         <v>1.81</v>
@@ -2583,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>108870</v>
+        <v>108861.28</v>
       </c>
       <c r="I26" t="n">
         <v>1.76</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Losuia Province</t>
+          <t>Milne Bay</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2651,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>103307.97</v>
+        <v>103303.89</v>
       </c>
       <c r="I27" t="n">
         <v>3.56</v>
@@ -2719,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>74809.22</v>
+        <v>74806.25999999999</v>
       </c>
       <c r="I28" t="n">
         <v>3.56</v>
@@ -2787,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>85496.25</v>
+        <v>85492.87</v>
       </c>
       <c r="I29" t="n">
         <v>3.56</v>
@@ -2855,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>49872.81</v>
+        <v>49870.84</v>
       </c>
       <c r="I30" t="n">
         <v>3.56</v>
@@ -2923,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>29851.45</v>
+        <v>29849.06</v>
       </c>
       <c r="I31" t="n">
         <v>1.76</v>
@@ -2991,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>53435.16</v>
+        <v>53433.05</v>
       </c>
       <c r="I32" t="n">
         <v>3.56</v>
@@ -3059,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>139009.8</v>
+        <v>138999.82</v>
       </c>
       <c r="I33" t="n">
         <v>1.96</v>
@@ -3127,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>43073.46</v>
+        <v>43070.37</v>
       </c>
       <c r="I34" t="n">
         <v>1.96</v>
@@ -3195,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>25452.5</v>
+        <v>25450.67</v>
       </c>
       <c r="I35" t="n">
         <v>1.96</v>
@@ -3263,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>110099.55</v>
+        <v>110098.15</v>
       </c>
       <c r="I36" t="n">
         <v>11.01</v>
@@ -3331,7 +3331,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>21536.73</v>
+        <v>21535.18</v>
       </c>
       <c r="I37" t="n">
         <v>1.96</v>
@@ -3399,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>27410.38</v>
+        <v>27408.41</v>
       </c>
       <c r="I38" t="n">
         <v>1.96</v>
@@ -3451,23 +3451,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Angau Province</t>
+          <t>Morobe</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>188000</v>
       </c>
       <c r="E39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="F39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>276276.52</v>
+        <v>276972.84</v>
       </c>
       <c r="I39" t="n">
         <v>1.47</v>
@@ -3491,7 +3491,7 @@
         <v>0.08</v>
       </c>
       <c r="N39" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
       <c r="O39" t="n">
         <v>0.0252</v>
@@ -3535,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>90408.16</v>
+        <v>90400.57000000001</v>
       </c>
       <c r="I40" t="n">
         <v>1.67</v>
@@ -3603,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>54377.48</v>
+        <v>54373.12</v>
       </c>
       <c r="I41" t="n">
         <v>1.75</v>
@@ -3671,7 +3671,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>80116.61</v>
+        <v>80110.7</v>
       </c>
       <c r="I42" t="n">
         <v>1.91</v>
@@ -3739,7 +3739,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>69125.32000000001</v>
+        <v>69120.25999999999</v>
       </c>
       <c r="I43" t="n">
         <v>1.92</v>
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>201596.42</v>
+        <v>201593.75</v>
       </c>
       <c r="I44" t="n">
         <v>10.61</v>
@@ -3875,7 +3875,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>32428.15</v>
+        <v>32425.76</v>
       </c>
       <c r="I45" t="n">
         <v>1.91</v>
@@ -3943,7 +3943,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>38022.74</v>
+        <v>38019.5</v>
       </c>
       <c r="I46" t="n">
         <v>1.65</v>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Modilon Province</t>
+          <t>Madang</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -4011,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>152093.53</v>
+        <v>152080.03</v>
       </c>
       <c r="I47" t="n">
         <v>1.58</v>
@@ -4079,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>84743.49000000001</v>
+        <v>84737.72</v>
       </c>
       <c r="I48" t="n">
         <v>2.07</v>
@@ -4147,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>58096.09</v>
+        <v>58092.43</v>
       </c>
       <c r="I49" t="n">
         <v>2.23</v>
@@ -4215,7 +4215,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>46934.85</v>
+        <v>46931.76</v>
       </c>
       <c r="I50" t="n">
         <v>2.13</v>
@@ -4283,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>53363.79</v>
+        <v>53359.85</v>
       </c>
       <c r="I51" t="n">
         <v>1.91</v>
@@ -4351,7 +4351,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>124693.02</v>
+        <v>124691.33</v>
       </c>
       <c r="I52" t="n">
         <v>10.39</v>
@@ -4482,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>185815.52</v>
+        <v>185803.14</v>
       </c>
       <c r="I54" t="n">
         <v>2.11</v>
@@ -4550,7 +4550,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>109800.08</v>
+        <v>109792.77</v>
       </c>
       <c r="I55" t="n">
         <v>2.11</v>
@@ -4618,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>92907.75999999999</v>
+        <v>92901.57000000001</v>
       </c>
       <c r="I56" t="n">
         <v>2.11</v>
@@ -4686,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>66036.32000000001</v>
+        <v>66032.95</v>
       </c>
       <c r="I57" t="n">
         <v>2.75</v>
@@ -4754,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>69680.82000000001</v>
+        <v>69676.17999999999</v>
       </c>
       <c r="I58" t="n">
         <v>2.11</v>
@@ -4822,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>57011.58</v>
+        <v>57007.78</v>
       </c>
       <c r="I59" t="n">
         <v>2.11</v>
@@ -4890,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>41272.7</v>
+        <v>41270.59</v>
       </c>
       <c r="I60" t="n">
         <v>2.75</v>
@@ -4958,7 +4958,7 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>99242.38</v>
+        <v>99235.77</v>
       </c>
       <c r="I61" t="n">
         <v>2.11</v>
@@ -5026,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>82350.06</v>
+        <v>82344.58</v>
       </c>
       <c r="I62" t="n">
         <v>2.11</v>
@@ -5094,7 +5094,7 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>50676.96</v>
+        <v>50673.58</v>
       </c>
       <c r="I63" t="n">
         <v>2.11</v>
@@ -5162,7 +5162,7 @@
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>46453.88</v>
+        <v>46450.79</v>
       </c>
       <c r="I64" t="n">
         <v>2.11</v>
@@ -5419,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>130754.87</v>
+        <v>130744.6</v>
       </c>
       <c r="I68" t="n">
         <v>1.82</v>
@@ -5487,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>83644.46000000001</v>
+        <v>83637.62</v>
       </c>
       <c r="I69" t="n">
         <v>1.74</v>
@@ -5555,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>74321.41</v>
+        <v>74315.99000000001</v>
       </c>
       <c r="I70" t="n">
         <v>1.96</v>
@@ -5623,7 +5623,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>85356.05</v>
+        <v>85350.2</v>
       </c>
       <c r="I71" t="n">
         <v>2.08</v>
@@ -5691,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>53616.83</v>
+        <v>53612.7</v>
       </c>
       <c r="I72" t="n">
         <v>1.85</v>
@@ -5759,7 +5759,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>60842.67</v>
+        <v>60838.11</v>
       </c>
       <c r="I73" t="n">
         <v>1.9</v>
@@ -5827,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>178857.91</v>
+        <v>178845.94</v>
       </c>
       <c r="I74" t="n">
         <v>2.13</v>
@@ -5895,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>95470.71000000001</v>
+        <v>95464.58</v>
       </c>
       <c r="I75" t="n">
         <v>2.22</v>
@@ -5963,7 +5963,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>67402.58</v>
+        <v>67398.16</v>
       </c>
       <c r="I76" t="n">
         <v>2.17</v>
@@ -6031,7 +6031,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>54866.14</v>
+        <v>54862.29</v>
       </c>
       <c r="I77" t="n">
         <v>2.03</v>
@@ -6162,7 +6162,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>144042.65</v>
+        <v>144031.39</v>
       </c>
       <c r="I79" t="n">
         <v>1.82</v>
@@ -6230,7 +6230,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>77985.64999999999</v>
+        <v>77979.37</v>
       </c>
       <c r="I80" t="n">
         <v>1.77</v>
@@ -6298,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>67569.63</v>
+        <v>67564.49000000001</v>
       </c>
       <c r="I81" t="n">
         <v>1.88</v>
@@ -6366,7 +6366,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>76404.49000000001</v>
+        <v>76398.92999999999</v>
       </c>
       <c r="I82" t="n">
         <v>1.96</v>
@@ -6434,7 +6434,7 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>44688.12</v>
+        <v>44684.84</v>
       </c>
       <c r="I83" t="n">
         <v>1.94</v>
@@ -6502,7 +6502,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>50837.48</v>
+        <v>50833.48</v>
       </c>
       <c r="I84" t="n">
         <v>1.82</v>
@@ -6570,7 +6570,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>179330.42</v>
+        <v>179314.45</v>
       </c>
       <c r="I85" t="n">
         <v>1.6</v>
@@ -6638,7 +6638,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>58742.21</v>
+        <v>58737.36</v>
       </c>
       <c r="I86" t="n">
         <v>1.73</v>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>54044.21</v>
+        <v>54039.79</v>
       </c>
       <c r="I87" t="n">
         <v>1.74</v>
@@ -6774,7 +6774,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>37042.63</v>
+        <v>37039.49</v>
       </c>
       <c r="I88" t="n">
         <v>1.68</v>
@@ -6842,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>42943.49</v>
+        <v>42939.79</v>
       </c>
       <c r="I89" t="n">
         <v>1.65</v>
@@ -6910,7 +6910,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>101267.36</v>
+        <v>101259.09</v>
       </c>
       <c r="I90" t="n">
         <v>1.75</v>
@@ -6978,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>70916.05</v>
+        <v>70910.2</v>
       </c>
       <c r="I91" t="n">
         <v>1.73</v>
@@ -7046,7 +7046,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>80711.78</v>
+        <v>80705.07000000001</v>
       </c>
       <c r="I92" t="n">
         <v>1.72</v>
@@ -7114,7 +7114,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>43573.48</v>
+        <v>43570.06</v>
       </c>
       <c r="I93" t="n">
         <v>1.82</v>
@@ -7182,7 +7182,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>196388.24</v>
+        <v>196385.53</v>
       </c>
       <c r="I94" t="n">
         <v>10.34</v>
@@ -7250,7 +7250,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>137209.96</v>
+        <v>137199.41</v>
       </c>
       <c r="I95" t="n">
         <v>1.85</v>
@@ -7318,7 +7318,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>82630.46000000001</v>
+        <v>82623.89999999999</v>
       </c>
       <c r="I96" t="n">
         <v>1.8</v>
@@ -7386,7 +7386,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>62470.35</v>
+        <v>62465.65</v>
       </c>
       <c r="I97" t="n">
         <v>1.89</v>
@@ -7454,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>221256.67</v>
+        <v>221253.68</v>
       </c>
       <c r="I98" t="n">
         <v>10.54</v>
@@ -7522,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>55509.53</v>
+        <v>55505.39</v>
       </c>
       <c r="I99" t="n">
         <v>1.91</v>
@@ -7590,7 +7590,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>48235.8</v>
+        <v>48232.24</v>
       </c>
       <c r="I100" t="n">
         <v>1.93</v>
@@ -7637,28 +7637,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Goroka Base Hospital</t>
+          <t>Goroka Provincial Hospital</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Goroka Province</t>
+          <t>Eastern Highlands</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>108000</v>
       </c>
       <c r="E101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="F101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>222975.13</v>
+        <v>222887.4</v>
       </c>
       <c r="I101" t="n">
         <v>2.06</v>
@@ -7726,7 +7726,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>116913.25</v>
+        <v>116904.53</v>
       </c>
       <c r="I102" t="n">
         <v>1.89</v>
@@ -7794,7 +7794,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>70425.71000000001</v>
+        <v>70420.92999999999</v>
       </c>
       <c r="I103" t="n">
         <v>2.07</v>
@@ -7862,7 +7862,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>68903.92</v>
+        <v>68899.56</v>
       </c>
       <c r="I104" t="n">
         <v>2.22</v>
@@ -7930,7 +7930,7 @@
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>58286.86</v>
+        <v>58282.92</v>
       </c>
       <c r="I105" t="n">
         <v>2.08</v>
@@ -8061,7 +8061,7 @@
         <v>0.8773</v>
       </c>
       <c r="H107" t="n">
-        <v>106246.07</v>
+        <v>106244.71</v>
       </c>
       <c r="I107" t="n">
         <v>9.66</v>
@@ -8129,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>94594.25999999999</v>
+        <v>94589.48</v>
       </c>
       <c r="I108" t="n">
         <v>2.78</v>
@@ -8197,7 +8197,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>25039.66</v>
+        <v>25038.39</v>
       </c>
       <c r="I109" t="n">
         <v>2.78</v>
@@ -8265,7 +8265,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>18084.2</v>
+        <v>18083.28</v>
       </c>
       <c r="I110" t="n">
         <v>2.78</v>
@@ -8333,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>15302.01</v>
+        <v>15301.24</v>
       </c>
       <c r="I111" t="n">
         <v>2.78</v>
@@ -8401,7 +8401,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>13910.92</v>
+        <v>13910.22</v>
       </c>
       <c r="I112" t="n">
         <v>2.78</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kavieng Province</t>
+          <t>New Ireland</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -8469,7 +8469,7 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>128459.48</v>
+        <v>128451.33</v>
       </c>
       <c r="I113" t="n">
         <v>2.21</v>
@@ -8537,7 +8537,7 @@
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>101881.66</v>
+        <v>101875.19</v>
       </c>
       <c r="I114" t="n">
         <v>2.21</v>
@@ -8605,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>43912.33</v>
+        <v>43909.66</v>
       </c>
       <c r="I115" t="n">
         <v>2.31</v>
@@ -8673,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>37651.92</v>
+        <v>37649.53</v>
       </c>
       <c r="I116" t="n">
         <v>2.21</v>
@@ -8741,7 +8741,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>18489.4</v>
+        <v>18488.28</v>
       </c>
       <c r="I117" t="n">
         <v>2.31</v>
@@ -8809,7 +8809,7 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>32356.45</v>
+        <v>32354.48</v>
       </c>
       <c r="I118" t="n">
         <v>2.31</v>
@@ -8877,7 +8877,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>161565.15</v>
+        <v>161552.22</v>
       </c>
       <c r="I119" t="n">
         <v>1.76</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>103320.49</v>
+        <v>103311.92</v>
       </c>
       <c r="I120" t="n">
         <v>1.69</v>
@@ -9013,7 +9013,7 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>67086.19</v>
+        <v>67080.85000000001</v>
       </c>
       <c r="I121" t="n">
         <v>1.77</v>
@@ -9081,7 +9081,7 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>36429.85</v>
+        <v>36426.9</v>
       </c>
       <c r="I122" t="n">
         <v>1.73</v>
@@ -9149,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>53985.93</v>
+        <v>53982.69</v>
       </c>
       <c r="I123" t="n">
         <v>2.35</v>
@@ -9217,7 +9217,7 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>42249.86</v>
+        <v>42247.33</v>
       </c>
       <c r="I124" t="n">
         <v>2.35</v>
@@ -9285,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>164344.34</v>
+        <v>164333.38</v>
       </c>
       <c r="I125" t="n">
         <v>2.11</v>
@@ -9353,7 +9353,7 @@
         <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>67423.32000000001</v>
+        <v>67418.82000000001</v>
       </c>
       <c r="I126" t="n">
         <v>2.11</v>
@@ -9421,7 +9421,7 @@
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>34964.62</v>
+        <v>34962.37</v>
       </c>
       <c r="I127" t="n">
         <v>2.19</v>
@@ -9489,7 +9489,7 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>86386.13</v>
+        <v>86380.36</v>
       </c>
       <c r="I128" t="n">
         <v>2.11</v>
@@ -9557,7 +9557,7 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>52446.93</v>
+        <v>52443.55</v>
       </c>
       <c r="I129" t="n">
         <v>2.19</v>
@@ -9625,7 +9625,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>155636.84</v>
+        <v>155627.42</v>
       </c>
       <c r="I130" t="n">
         <v>2.32</v>
@@ -9693,7 +9693,7 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>120792.77</v>
+        <v>120785.46</v>
       </c>
       <c r="I131" t="n">
         <v>2.32</v>
@@ -9761,7 +9761,7 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>102209.27</v>
+        <v>102203.08</v>
       </c>
       <c r="I132" t="n">
         <v>2.32</v>
@@ -9829,7 +9829,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>41812.88</v>
+        <v>41810.35</v>
       </c>
       <c r="I133" t="n">
         <v>2.32</v>
@@ -9897,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>16260.57</v>
+        <v>16259.58</v>
       </c>
       <c r="I134" t="n">
         <v>2.32</v>
@@ -9965,7 +9965,7 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>37167.01</v>
+        <v>37164.76</v>
       </c>
       <c r="I135" t="n">
         <v>2.32</v>
@@ -10144,7 +10144,7 @@
         <v>2721.52</v>
       </c>
       <c r="I2" t="n">
-        <v>114313.66</v>
+        <v>114313.64</v>
       </c>
       <c r="J2" t="n">
         <v>100.39</v>
@@ -10196,7 +10196,7 @@
         <v>195.25</v>
       </c>
       <c r="I3" t="n">
-        <v>14351.99</v>
+        <v>14351.95</v>
       </c>
       <c r="J3" t="n">
         <v>322.81</v>
@@ -10254,7 +10254,7 @@
         <v>195.25</v>
       </c>
       <c r="I4" t="n">
-        <v>21869.71</v>
+        <v>21869.64</v>
       </c>
       <c r="J4" t="n">
         <v>483.47</v>
@@ -10312,7 +10312,7 @@
         <v>195.25</v>
       </c>
       <c r="I5" t="n">
-        <v>12301.71</v>
+        <v>12301.67</v>
       </c>
       <c r="J5" t="n">
         <v>416.21</v>
@@ -10370,7 +10370,7 @@
         <v>216.81</v>
       </c>
       <c r="I6" t="n">
-        <v>33390.95</v>
+        <v>33390.86</v>
       </c>
       <c r="J6" t="n">
         <v>538.08</v>
@@ -10428,7 +10428,7 @@
         <v>200.68</v>
       </c>
       <c r="I7" t="n">
-        <v>27395.49</v>
+        <v>27395.41</v>
       </c>
       <c r="J7" t="n">
         <v>1162.1</v>
@@ -10486,7 +10486,7 @@
         <v>200.68</v>
       </c>
       <c r="I8" t="n">
-        <v>19668.56</v>
+        <v>19668.5</v>
       </c>
       <c r="J8" t="n">
         <v>1251.46</v>
@@ -10544,7 +10544,7 @@
         <v>200.68</v>
       </c>
       <c r="I9" t="n">
-        <v>21775.9</v>
+        <v>21775.84</v>
       </c>
       <c r="J9" t="n">
         <v>767.52</v>
@@ -10602,7 +10602,7 @@
         <v>200.68</v>
       </c>
       <c r="I10" t="n">
-        <v>5268.36</v>
+        <v>5268.35</v>
       </c>
       <c r="J10" t="n">
         <v>955.4400000000001</v>
@@ -10660,7 +10660,7 @@
         <v>2776.94</v>
       </c>
       <c r="I11" t="n">
-        <v>87481.02</v>
+        <v>87481</v>
       </c>
       <c r="J11" t="n">
         <v>617.75</v>
@@ -10712,7 +10712,7 @@
         <v>2776.94</v>
       </c>
       <c r="I12" t="n">
-        <v>82620.96000000001</v>
+        <v>82620.95</v>
       </c>
       <c r="J12" t="n">
         <v>684.9400000000001</v>
@@ -10764,7 +10764,7 @@
         <v>186.08</v>
       </c>
       <c r="I13" t="n">
-        <v>40383.81</v>
+        <v>40383.69</v>
       </c>
       <c r="J13" t="n">
         <v>448.61</v>
@@ -10822,7 +10822,7 @@
         <v>186.08</v>
       </c>
       <c r="I14" t="n">
-        <v>11072.98</v>
+        <v>11072.95</v>
       </c>
       <c r="J14" t="n">
         <v>358.09</v>
@@ -10880,7 +10880,7 @@
         <v>702.15</v>
       </c>
       <c r="I15" t="n">
-        <v>71274.10000000001</v>
+        <v>71274.05</v>
       </c>
       <c r="J15" t="n">
         <v>534.23</v>
@@ -10938,7 +10938,7 @@
         <v>702.15</v>
       </c>
       <c r="I16" t="n">
-        <v>51612.28</v>
+        <v>51612.24</v>
       </c>
       <c r="J16" t="n">
         <v>758.5700000000001</v>
@@ -10996,7 +10996,7 @@
         <v>702.15</v>
       </c>
       <c r="I17" t="n">
-        <v>58985.47</v>
+        <v>58985.42</v>
       </c>
       <c r="J17" t="n">
         <v>483.91</v>
@@ -11054,7 +11054,7 @@
         <v>702.15</v>
       </c>
       <c r="I18" t="n">
-        <v>34408.19</v>
+        <v>34408.16</v>
       </c>
       <c r="J18" t="n">
         <v>488.03</v>
@@ -11112,7 +11112,7 @@
         <v>702.15</v>
       </c>
       <c r="I19" t="n">
-        <v>36865.92</v>
+        <v>36865.89</v>
       </c>
       <c r="J19" t="n">
         <v>407.1</v>
@@ -11170,7 +11170,7 @@
         <v>243.77</v>
       </c>
       <c r="I20" t="n">
-        <v>60582.07</v>
+        <v>60581.93</v>
       </c>
       <c r="J20" t="n">
         <v>323.36</v>
@@ -11228,7 +11228,7 @@
         <v>243.77</v>
       </c>
       <c r="I21" t="n">
-        <v>18771.91</v>
+        <v>18771.86</v>
       </c>
       <c r="J21" t="n">
         <v>308.79</v>
@@ -11286,7 +11286,7 @@
         <v>243.77</v>
       </c>
       <c r="I22" t="n">
-        <v>11092.49</v>
+        <v>11092.47</v>
       </c>
       <c r="J22" t="n">
         <v>447.3</v>
@@ -11344,7 +11344,7 @@
         <v>243.77</v>
       </c>
       <c r="I23" t="n">
-        <v>9385.950000000001</v>
+        <v>9385.93</v>
       </c>
       <c r="J23" t="n">
         <v>459</v>
@@ -11402,7 +11402,7 @@
         <v>243.77</v>
       </c>
       <c r="I24" t="n">
-        <v>11945.76</v>
+        <v>11945.73</v>
       </c>
       <c r="J24" t="n">
         <v>306.91</v>
@@ -11460,7 +11460,7 @@
         <v>2829.85</v>
       </c>
       <c r="I25" t="n">
-        <v>99053.39999999999</v>
+        <v>99053.38</v>
       </c>
       <c r="J25" t="n">
         <v>315.98</v>
@@ -11512,7 +11512,7 @@
         <v>229.39</v>
       </c>
       <c r="I26" t="n">
-        <v>33722.74</v>
+        <v>33722.65</v>
       </c>
       <c r="J26" t="n">
         <v>117.11</v>
@@ -11570,7 +11570,7 @@
         <v>229.39</v>
       </c>
       <c r="I27" t="n">
-        <v>13649.68</v>
+        <v>13649.65</v>
       </c>
       <c r="J27" t="n">
         <v>106.12</v>
@@ -11628,7 +11628,7 @@
         <v>2715.69</v>
       </c>
       <c r="I28" t="n">
-        <v>180608.72</v>
+        <v>180608.68</v>
       </c>
       <c r="J28" t="n">
         <v>64.55</v>
@@ -11680,7 +11680,7 @@
         <v>322.79</v>
       </c>
       <c r="I29" t="n">
-        <v>29376.07</v>
+        <v>29376.02</v>
       </c>
       <c r="J29" t="n">
         <v>106.06</v>
@@ -11738,7 +11738,7 @@
         <v>293.91</v>
       </c>
       <c r="I30" t="n">
-        <v>22633.3</v>
+        <v>22633.26</v>
       </c>
       <c r="J30" t="n">
         <v>80.93000000000001</v>
@@ -11796,7 +11796,7 @@
         <v>2653.05</v>
       </c>
       <c r="I31" t="n">
-        <v>111437.63</v>
+        <v>111437.6</v>
       </c>
       <c r="J31" t="n">
         <v>98.78</v>
@@ -11848,7 +11848,7 @@
         <v>287.67</v>
       </c>
       <c r="I32" t="n">
-        <v>88609.32000000001</v>
+        <v>88609.14</v>
       </c>
       <c r="J32" t="n">
         <v>364.01</v>
@@ -11906,7 +11906,7 @@
         <v>287.67</v>
       </c>
       <c r="I33" t="n">
-        <v>52360.05</v>
+        <v>52359.95</v>
       </c>
       <c r="J33" t="n">
         <v>428.56</v>
@@ -11964,7 +11964,7 @@
         <v>287.67</v>
       </c>
       <c r="I34" t="n">
-        <v>44304.66</v>
+        <v>44304.57</v>
       </c>
       <c r="J34" t="n">
         <v>280.66</v>
@@ -12022,7 +12022,7 @@
         <v>287.67</v>
       </c>
       <c r="I35" t="n">
-        <v>33228.49</v>
+        <v>33228.43</v>
       </c>
       <c r="J35" t="n">
         <v>390.59</v>
@@ -12080,7 +12080,7 @@
         <v>287.67</v>
       </c>
       <c r="I36" t="n">
-        <v>27186.95</v>
+        <v>27186.9</v>
       </c>
       <c r="J36" t="n">
         <v>405.44</v>
@@ -12138,7 +12138,7 @@
         <v>287.67</v>
       </c>
       <c r="I37" t="n">
-        <v>47325.43</v>
+        <v>47325.34</v>
       </c>
       <c r="J37" t="n">
         <v>698.29</v>
@@ -12196,7 +12196,7 @@
         <v>287.67</v>
       </c>
       <c r="I38" t="n">
-        <v>39270.04</v>
+        <v>39269.96</v>
       </c>
       <c r="J38" t="n">
         <v>544.61</v>
@@ -12254,7 +12254,7 @@
         <v>287.67</v>
       </c>
       <c r="I39" t="n">
-        <v>24166.18</v>
+        <v>24166.13</v>
       </c>
       <c r="J39" t="n">
         <v>560.1</v>
@@ -12312,7 +12312,7 @@
         <v>287.67</v>
       </c>
       <c r="I40" t="n">
-        <v>22152.33</v>
+        <v>22152.29</v>
       </c>
       <c r="J40" t="n">
         <v>494.37</v>
@@ -12370,7 +12370,7 @@
         <v>470.5</v>
       </c>
       <c r="I41" t="n">
-        <v>39525.54</v>
+        <v>39525.49</v>
       </c>
       <c r="J41" t="n">
         <v>532.85</v>
@@ -12428,7 +12428,7 @@
         <v>470.5</v>
       </c>
       <c r="I42" t="n">
-        <v>24703.46</v>
+        <v>24703.43</v>
       </c>
       <c r="J42" t="n">
         <v>426.83</v>
@@ -12483,10 +12483,10 @@
         <v>66.5057</v>
       </c>
       <c r="H43" t="n">
-        <v>2637.38</v>
+        <v>2637.37</v>
       </c>
       <c r="I43" t="n">
-        <v>175400.54</v>
+        <v>175400.46</v>
       </c>
       <c r="J43" t="n">
         <v>53.72</v>
@@ -12538,7 +12538,7 @@
         <v>2694.46</v>
       </c>
       <c r="I44" t="n">
-        <v>198059.74</v>
+        <v>198059.65</v>
       </c>
       <c r="J44" t="n">
         <v>94.98999999999999</v>
@@ -12590,7 +12590,7 @@
         <v>2829.85</v>
       </c>
       <c r="I45" t="n">
-        <v>95586.53</v>
+        <v>95586.50999999999</v>
       </c>
       <c r="J45" t="n">
         <v>130.5</v>
@@ -12642,7 +12642,7 @@
         <v>479.26</v>
       </c>
       <c r="I46" t="n">
-        <v>57037.32</v>
+        <v>57037.25</v>
       </c>
       <c r="J46" t="n">
         <v>477.86</v>
@@ -12700,7 +12700,7 @@
         <v>479.26</v>
       </c>
       <c r="I47" t="n">
-        <v>15098.11</v>
+        <v>15098.1</v>
       </c>
       <c r="J47" t="n">
         <v>482.12</v>
@@ -12758,7 +12758,7 @@
         <v>479.26</v>
       </c>
       <c r="I48" t="n">
-        <v>10904.19</v>
+        <v>10904.18</v>
       </c>
       <c r="J48" t="n">
         <v>480.24</v>
@@ -12816,7 +12816,7 @@
         <v>479.26</v>
       </c>
       <c r="I49" t="n">
-        <v>9226.620000000001</v>
+        <v>9226.610000000001</v>
       </c>
       <c r="J49" t="n">
         <v>481.26</v>
@@ -12874,7 +12874,7 @@
         <v>479.26</v>
       </c>
       <c r="I50" t="n">
-        <v>8387.84</v>
+        <v>8387.83</v>
       </c>
       <c r="J50" t="n">
         <v>412.79</v>
@@ -12932,7 +12932,7 @@
         <v>317.17</v>
       </c>
       <c r="I51" t="n">
-        <v>64391.76</v>
+        <v>64391.64</v>
       </c>
       <c r="J51" t="n">
         <v>311.37</v>
@@ -12990,7 +12990,7 @@
         <v>317.17</v>
       </c>
       <c r="I52" t="n">
-        <v>51069.33</v>
+        <v>51069.23</v>
       </c>
       <c r="J52" t="n">
         <v>94.95999999999999</v>
@@ -13048,7 +13048,7 @@
         <v>344.7</v>
       </c>
       <c r="I53" t="n">
-        <v>22924.63</v>
+        <v>22924.59</v>
       </c>
       <c r="J53" t="n">
         <v>182.8</v>
@@ -13106,7 +13106,7 @@
         <v>317.17</v>
       </c>
       <c r="I54" t="n">
-        <v>18873.45</v>
+        <v>18873.41</v>
       </c>
       <c r="J54" t="n">
         <v>175.95</v>
@@ -13164,7 +13164,7 @@
         <v>344.7</v>
       </c>
       <c r="I55" t="n">
-        <v>9652.469999999999</v>
+        <v>9652.459999999999</v>
       </c>
       <c r="J55" t="n">
         <v>205.12</v>
@@ -13222,7 +13222,7 @@
         <v>344.7</v>
       </c>
       <c r="I56" t="n">
-        <v>16891.83</v>
+        <v>16891.8</v>
       </c>
       <c r="J56" t="n">
         <v>368.78</v>
@@ -13280,7 +13280,7 @@
         <v>355</v>
       </c>
       <c r="I57" t="n">
-        <v>28579.76</v>
+        <v>28579.72</v>
       </c>
       <c r="J57" t="n">
         <v>240.83</v>
@@ -13338,7 +13338,7 @@
         <v>355</v>
       </c>
       <c r="I58" t="n">
-        <v>22366.77</v>
+        <v>22366.73</v>
       </c>
       <c r="J58" t="n">
         <v>189.94</v>
@@ -13396,7 +13396,7 @@
         <v>286.36</v>
       </c>
       <c r="I59" t="n">
-        <v>78184.3</v>
+        <v>78184.14999999999</v>
       </c>
       <c r="J59" t="n">
         <v>328.7</v>
@@ -13454,7 +13454,7 @@
         <v>286.36</v>
       </c>
       <c r="I60" t="n">
-        <v>32075.61</v>
+        <v>32075.55</v>
       </c>
       <c r="J60" t="n">
         <v>328.88</v>
@@ -13512,7 +13512,7 @@
         <v>308.74</v>
       </c>
       <c r="I61" t="n">
-        <v>17290.76</v>
+        <v>17290.73</v>
       </c>
       <c r="J61" t="n">
         <v>369.95</v>
@@ -13570,7 +13570,7 @@
         <v>286.36</v>
       </c>
       <c r="I62" t="n">
-        <v>41096.88</v>
+        <v>41096.8</v>
       </c>
       <c r="J62" t="n">
         <v>215.37</v>
@@ -13628,7 +13628,7 @@
         <v>308.74</v>
       </c>
       <c r="I63" t="n">
-        <v>25936.15</v>
+        <v>25936.1</v>
       </c>
       <c r="J63" t="n">
         <v>445.5</v>
@@ -13686,7 +13686,7 @@
         <v>348.06</v>
       </c>
       <c r="I64" t="n">
-        <v>81627.58</v>
+        <v>81627.44</v>
       </c>
       <c r="J64" t="n">
         <v>357.34</v>
@@ -13744,7 +13744,7 @@
         <v>348.06</v>
       </c>
       <c r="I65" t="n">
-        <v>63352.75</v>
+        <v>63352.64</v>
       </c>
       <c r="J65" t="n">
         <v>513.78</v>
@@ -13802,7 +13802,7 @@
         <v>348.06</v>
       </c>
       <c r="I66" t="n">
-        <v>53606.17</v>
+        <v>53606.08</v>
       </c>
       <c r="J66" t="n">
         <v>577.77</v>
@@ -13860,7 +13860,7 @@
         <v>348.06</v>
       </c>
       <c r="I67" t="n">
-        <v>21929.8</v>
+        <v>21929.76</v>
       </c>
       <c r="J67" t="n">
         <v>447.68</v>
@@ -13918,7 +13918,7 @@
         <v>348.06</v>
       </c>
       <c r="I68" t="n">
-        <v>8528.25</v>
+        <v>8528.24</v>
       </c>
       <c r="J68" t="n">
         <v>267.72</v>
@@ -13976,7 +13976,7 @@
         <v>348.06</v>
       </c>
       <c r="I69" t="n">
-        <v>19493.15</v>
+        <v>19493.12</v>
       </c>
       <c r="J69" t="n">
         <v>370.08</v>
@@ -14028,13 +14028,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>587.5544</v>
+        <v>588.0504</v>
       </c>
       <c r="H70" t="n">
         <v>55.64</v>
       </c>
       <c r="I70" t="n">
-        <v>32691.99</v>
+        <v>32716.97</v>
       </c>
       <c r="J70" t="n">
         <v>4.28</v>
@@ -14083,10 +14083,10 @@
         <v>462.0396</v>
       </c>
       <c r="H71" t="n">
-        <v>60.04</v>
+        <v>60.03</v>
       </c>
       <c r="I71" t="n">
-        <v>27738.74</v>
+        <v>27738.47</v>
       </c>
       <c r="J71" t="n">
         <v>13.54</v>
@@ -14138,7 +14138,7 @@
         <v>54.32</v>
       </c>
       <c r="I72" t="n">
-        <v>11598.56</v>
+        <v>11598.44</v>
       </c>
       <c r="J72" t="n">
         <v>1.51</v>
@@ -14190,7 +14190,7 @@
         <v>56.12</v>
       </c>
       <c r="I73" t="n">
-        <v>10606.96</v>
+        <v>10606.85</v>
       </c>
       <c r="J73" t="n">
         <v>5.29</v>
@@ -14242,7 +14242,7 @@
         <v>58.93</v>
       </c>
       <c r="I74" t="n">
-        <v>7838.18</v>
+        <v>7838.11</v>
       </c>
       <c r="J74" t="n">
         <v>11.21</v>
@@ -14294,7 +14294,7 @@
         <v>110.15</v>
       </c>
       <c r="I75" t="n">
-        <v>18120.56</v>
+        <v>18120.47</v>
       </c>
       <c r="J75" t="n">
         <v>103.3</v>
@@ -14346,7 +14346,7 @@
         <v>171.81</v>
       </c>
       <c r="I76" t="n">
-        <v>25258.54</v>
+        <v>25258.46</v>
       </c>
       <c r="J76" t="n">
         <v>171.76</v>
@@ -14398,7 +14398,7 @@
         <v>187.28</v>
       </c>
       <c r="I77" t="n">
-        <v>12455.07</v>
+        <v>12455.04</v>
       </c>
       <c r="J77" t="n">
         <v>218.82</v>
@@ -14450,7 +14450,7 @@
         <v>152.79</v>
       </c>
       <c r="I78" t="n">
-        <v>20322.3</v>
+        <v>20322.22</v>
       </c>
       <c r="J78" t="n">
         <v>183.69</v>
@@ -14502,7 +14502,7 @@
         <v>141.81</v>
       </c>
       <c r="I79" t="n">
-        <v>7941.95</v>
+        <v>7941.92</v>
       </c>
       <c r="J79" t="n">
         <v>125.96</v>
@@ -14554,7 +14554,7 @@
         <v>231.01</v>
       </c>
       <c r="I80" t="n">
-        <v>46899.45</v>
+        <v>46899.34</v>
       </c>
       <c r="J80" t="n">
         <v>331.17</v>
@@ -14606,7 +14606,7 @@
         <v>240.29</v>
       </c>
       <c r="I81" t="n">
-        <v>20186.1</v>
+        <v>20186.05</v>
       </c>
       <c r="J81" t="n">
         <v>276.29</v>
@@ -14652,13 +14652,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>656.3203999999999</v>
+        <v>658.0564000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>105.37</v>
+        <v>105.36</v>
       </c>
       <c r="I82" t="n">
-        <v>69156.57000000001</v>
+        <v>69331.11</v>
       </c>
       <c r="J82" t="n">
         <v>1.06</v>
@@ -14710,7 +14710,7 @@
         <v>162.73</v>
       </c>
       <c r="I83" t="n">
-        <v>30758.9</v>
+        <v>30758.79</v>
       </c>
       <c r="J83" t="n">
         <v>113.39</v>
@@ -14762,7 +14762,7 @@
         <v>185.55</v>
       </c>
       <c r="I84" t="n">
-        <v>20134.38</v>
+        <v>20134.32</v>
       </c>
       <c r="J84" t="n">
         <v>129.6</v>
@@ -14814,7 +14814,7 @@
         <v>232.99</v>
       </c>
       <c r="I85" t="n">
-        <v>29359.15</v>
+        <v>29359.08</v>
       </c>
       <c r="J85" t="n">
         <v>209.49</v>
@@ -14866,7 +14866,7 @@
         <v>156.71</v>
       </c>
       <c r="I86" t="n">
-        <v>12616.57</v>
+        <v>12616.52</v>
       </c>
       <c r="J86" t="n">
         <v>101.42</v>
@@ -14918,7 +14918,7 @@
         <v>137.04</v>
       </c>
       <c r="I87" t="n">
-        <v>46050.4</v>
+        <v>46050.21</v>
       </c>
       <c r="J87" t="n">
         <v>1.39</v>
@@ -14970,7 +14970,7 @@
         <v>274.92</v>
       </c>
       <c r="I88" t="n">
-        <v>39454.23</v>
+        <v>39454.15</v>
       </c>
       <c r="J88" t="n">
         <v>202.79</v>
@@ -15022,7 +15022,7 @@
         <v>228.9</v>
       </c>
       <c r="I89" t="n">
-        <v>22434.55</v>
+        <v>22434.49</v>
       </c>
       <c r="J89" t="n">
         <v>132.55</v>
@@ -15074,7 +15074,7 @@
         <v>203.25</v>
       </c>
       <c r="I90" t="n">
-        <v>51222.52</v>
+        <v>51222.24</v>
       </c>
       <c r="J90" t="n">
         <v>122.66</v>
@@ -15126,7 +15126,7 @@
         <v>182.26</v>
       </c>
       <c r="I91" t="n">
-        <v>30622.9</v>
+        <v>30622.71</v>
       </c>
       <c r="J91" t="n">
         <v>80.92</v>
@@ -15178,7 +15178,7 @@
         <v>243.18</v>
       </c>
       <c r="I92" t="n">
-        <v>32346</v>
+        <v>32345.85</v>
       </c>
       <c r="J92" t="n">
         <v>166.27</v>
@@ -15230,7 +15230,7 @@
         <v>279.19</v>
       </c>
       <c r="I93" t="n">
-        <v>40066.79</v>
+        <v>40066.63</v>
       </c>
       <c r="J93" t="n">
         <v>226.91</v>
@@ -15282,7 +15282,7 @@
         <v>212.62</v>
       </c>
       <c r="I94" t="n">
-        <v>21582.97</v>
+        <v>21582.85</v>
       </c>
       <c r="J94" t="n">
         <v>114.8</v>
@@ -15334,7 +15334,7 @@
         <v>227.61</v>
       </c>
       <c r="I95" t="n">
-        <v>25494.96</v>
+        <v>25494.83</v>
       </c>
       <c r="J95" t="n">
         <v>140.05</v>
@@ -15386,7 +15386,7 @@
         <v>292.73</v>
       </c>
       <c r="I96" t="n">
-        <v>86070.17999999999</v>
+        <v>86069.84</v>
       </c>
       <c r="J96" t="n">
         <v>249.72</v>
@@ -15438,7 +15438,7 @@
         <v>318.72</v>
       </c>
       <c r="I97" t="n">
-        <v>47972.22</v>
+        <v>47972.05</v>
       </c>
       <c r="J97" t="n">
         <v>293.5</v>
@@ -15490,7 +15490,7 @@
         <v>305.59</v>
       </c>
       <c r="I98" t="n">
-        <v>33159.49</v>
+        <v>33159.37</v>
       </c>
       <c r="J98" t="n">
         <v>271.38</v>
@@ -15542,7 +15542,7 @@
         <v>264.97</v>
       </c>
       <c r="I99" t="n">
-        <v>25041.51</v>
+        <v>25041.41</v>
       </c>
       <c r="J99" t="n">
         <v>202.96</v>
@@ -15594,7 +15594,7 @@
         <v>205.33</v>
       </c>
       <c r="I100" t="n">
-        <v>56778</v>
+        <v>56777.68</v>
       </c>
       <c r="J100" t="n">
         <v>126.8</v>
@@ -15646,7 +15646,7 @@
         <v>190.78</v>
       </c>
       <c r="I101" t="n">
-        <v>29382.55</v>
+        <v>29382.37</v>
       </c>
       <c r="J101" t="n">
         <v>97.86</v>
@@ -15698,7 +15698,7 @@
         <v>220.64</v>
       </c>
       <c r="I102" t="n">
-        <v>27803.45</v>
+        <v>27803.31</v>
       </c>
       <c r="J102" t="n">
         <v>128.31</v>
@@ -15750,7 +15750,7 @@
         <v>244.11</v>
       </c>
       <c r="I103" t="n">
-        <v>33324.47</v>
+        <v>33324.31</v>
       </c>
       <c r="J103" t="n">
         <v>167.84</v>
@@ -15802,7 +15802,7 @@
         <v>239.51</v>
       </c>
       <c r="I104" t="n">
-        <v>19281.95</v>
+        <v>19281.86</v>
       </c>
       <c r="J104" t="n">
         <v>160.08</v>
@@ -15854,7 +15854,7 @@
         <v>203.13</v>
       </c>
       <c r="I105" t="n">
-        <v>19908.23</v>
+        <v>19908.12</v>
       </c>
       <c r="J105" t="n">
         <v>98.81</v>
@@ -15906,7 +15906,7 @@
         <v>141.86</v>
       </c>
       <c r="I106" t="n">
-        <v>55613.44</v>
+        <v>55613</v>
       </c>
       <c r="J106" t="n">
         <v>2.42</v>
@@ -15958,7 +15958,7 @@
         <v>178.01</v>
       </c>
       <c r="I107" t="n">
-        <v>21185.26</v>
+        <v>21185.13</v>
       </c>
       <c r="J107" t="n">
         <v>56.51</v>
@@ -16010,7 +16010,7 @@
         <v>182.48</v>
       </c>
       <c r="I108" t="n">
-        <v>19801.11</v>
+        <v>19800.99</v>
       </c>
       <c r="J108" t="n">
         <v>64.04000000000001</v>
@@ -16062,7 +16062,7 @@
         <v>165.45</v>
       </c>
       <c r="I109" t="n">
-        <v>12741.08</v>
+        <v>12740.99</v>
       </c>
       <c r="J109" t="n">
         <v>35.36</v>
@@ -16114,7 +16114,7 @@
         <v>156.29</v>
       </c>
       <c r="I110" t="n">
-        <v>14223.48</v>
+        <v>14223.38</v>
       </c>
       <c r="J110" t="n">
         <v>29.25</v>
@@ -16166,7 +16166,7 @@
         <v>183.23</v>
       </c>
       <c r="I111" t="n">
-        <v>37199.64</v>
+        <v>37199.41</v>
       </c>
       <c r="J111" t="n">
         <v>82.84999999999999</v>
@@ -16218,7 +16218,7 @@
         <v>178.57</v>
       </c>
       <c r="I112" t="n">
-        <v>25626.79</v>
+        <v>25626.63</v>
       </c>
       <c r="J112" t="n">
         <v>73.56999999999999</v>
@@ -16270,7 +16270,7 @@
         <v>175.03</v>
       </c>
       <c r="I113" t="n">
-        <v>28794.83</v>
+        <v>28794.64</v>
       </c>
       <c r="J113" t="n">
         <v>66.53</v>
@@ -16322,7 +16322,7 @@
         <v>203.11</v>
       </c>
       <c r="I114" t="n">
-        <v>17062.7</v>
+        <v>17062.61</v>
       </c>
       <c r="J114" t="n">
         <v>98.78</v>
@@ -16371,10 +16371,10 @@
         <v>259.0222</v>
       </c>
       <c r="H115" t="n">
-        <v>214.15</v>
+        <v>214.14</v>
       </c>
       <c r="I115" t="n">
-        <v>55468.38</v>
+        <v>55468.09</v>
       </c>
       <c r="J115" t="n">
         <v>144.34</v>
@@ -16426,7 +16426,7 @@
         <v>197.61</v>
       </c>
       <c r="I116" t="n">
-        <v>31818.13</v>
+        <v>31817.95</v>
       </c>
       <c r="J116" t="n">
         <v>111.45</v>
@@ -16478,7 +16478,7 @@
         <v>225.24</v>
       </c>
       <c r="I117" t="n">
-        <v>26018.03</v>
+        <v>26017.89</v>
       </c>
       <c r="J117" t="n">
         <v>136.06</v>
@@ -16530,7 +16530,7 @@
         <v>231.27</v>
       </c>
       <c r="I118" t="n">
-        <v>23475.67</v>
+        <v>23475.55</v>
       </c>
       <c r="J118" t="n">
         <v>178.4</v>
@@ -16582,7 +16582,7 @@
         <v>235.64</v>
       </c>
       <c r="I119" t="n">
-        <v>20620.4</v>
+        <v>20620.3</v>
       </c>
       <c r="J119" t="n">
         <v>153.57</v>
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>378.1564</v>
+        <v>378.0324</v>
       </c>
       <c r="H120" t="n">
         <v>274.06</v>
       </c>
       <c r="I120" t="n">
-        <v>103637.48</v>
+        <v>103603.85</v>
       </c>
       <c r="J120" t="n">
         <v>334.85</v>
@@ -16686,7 +16686,7 @@
         <v>223.15</v>
       </c>
       <c r="I121" t="n">
-        <v>48427.06</v>
+        <v>48426.94</v>
       </c>
       <c r="J121" t="n">
         <v>233.57</v>
@@ -16738,7 +16738,7 @@
         <v>276.18</v>
       </c>
       <c r="I122" t="n">
-        <v>32868.77</v>
+        <v>32868.7</v>
       </c>
       <c r="J122" t="n">
         <v>282.24</v>
@@ -16790,7 +16790,7 @@
         <v>319.43</v>
       </c>
       <c r="I123" t="n">
-        <v>34660.83</v>
+        <v>34660.77</v>
       </c>
       <c r="J123" t="n">
         <v>355.07</v>
@@ -16839,10 +16839,10 @@
         <v>98.00839999999999</v>
       </c>
       <c r="H124" t="n">
-        <v>279.14</v>
+        <v>279.13</v>
       </c>
       <c r="I124" t="n">
-        <v>27357.61</v>
+        <v>27357.56</v>
       </c>
       <c r="J124" t="n">
         <v>287.21</v>
@@ -16894,7 +16894,7 @@
         <v>186.13</v>
       </c>
       <c r="I125" t="n">
-        <v>59940.49</v>
+        <v>59940.31</v>
       </c>
       <c r="J125" t="n">
         <v>31.5</v>
@@ -16946,7 +16946,7 @@
         <v>168.32</v>
       </c>
       <c r="I126" t="n">
-        <v>35938.92</v>
+        <v>35938.8</v>
       </c>
       <c r="J126" t="n">
         <v>1.35</v>
@@ -16998,7 +16998,7 @@
         <v>188.79</v>
       </c>
       <c r="I127" t="n">
-        <v>25110.79</v>
+        <v>25110.71</v>
       </c>
       <c r="J127" t="n">
         <v>36.5</v>
@@ -17050,7 +17050,7 @@
         <v>180.02</v>
       </c>
       <c r="I128" t="n">
-        <v>13232.92</v>
+        <v>13232.87</v>
       </c>
       <c r="J128" t="n">
         <v>19.98</v>
@@ -17164,16 +17164,16 @@
         <v>1034000</v>
       </c>
       <c r="D5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1549103.06</v>
+        <v>1549862.25</v>
       </c>
       <c r="H5" t="n">
         <v>1.5</v>
@@ -17204,7 +17204,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1712546.1</v>
+        <v>1712415</v>
       </c>
       <c r="H6" t="n">
         <v>1.85</v>
@@ -17235,7 +17235,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1862629.21</v>
+        <v>1862488.08</v>
       </c>
       <c r="H7" t="n">
         <v>1.87</v>
@@ -17257,16 +17257,16 @@
         <v>967500</v>
       </c>
       <c r="D8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2076990.69</v>
+        <v>2076781.65</v>
       </c>
       <c r="H8" t="n">
         <v>2.15</v>
@@ -17297,7 +17297,7 @@
         <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>2998941.6</v>
+        <v>2998818.33</v>
       </c>
       <c r="H9" t="n">
         <v>3.08</v>
@@ -17329,7 +17329,7 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="36" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="49" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17342,7 +17342,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>One-off cost 0 PGK · annual change -5,068,938 PGK · payback n/a years</t>
+          <t>One-off cost 0 PGK · annual change -1,043,813 PGK · payback n/a years</t>
         </is>
       </c>
     </row>
@@ -17429,7 +17429,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-5068938.23</v>
+        <v>-1043813.17</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Worst-quintile fill rate moves from 66% to 90%.</t>
+          <t>Worst-quintile fill rate moves from 100% to 90%.</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 74 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 47 ms</t>
         </is>
       </c>
     </row>
@@ -798,6 +798,157 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Share of demand volume that is estimated</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Facilities with estimated demand</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>134</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8730255.720000001</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>11723958.94</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9684</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 47 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:50 UTC · 61 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:50 UTC · 61 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 49 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 49 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 51 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 51 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 55 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 55 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 70 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 70 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 187 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 187 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 171 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 171 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 176 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 176 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 81 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 81 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 148 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 148 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 48 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-3.xlsx
+++ b/docs/app/api/files/results-3.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 48 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:14 UTC · 51 ms</t>
         </is>
       </c>
     </row>
